--- a/6ch_LED_Driver/Map Registers Control_LED.xlsx
+++ b/6ch_LED_Driver/Map Registers Control_LED.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927F91C3-0791-498F-8134-5423DE698A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BAF8ED2-3083-4BEC-B25B-812430A44409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>Десятичная</t>
   </si>
@@ -596,6 +596,18 @@
 A1 -0
 D - 0
 N1 - 0</t>
+  </si>
+  <si>
+    <t>0x14</t>
+  </si>
+  <si>
+    <t>Калибровка нуля датчика тока</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+C20A0D0N0x` - выполнить калибровку нуля (при отключенной нагрузке)
+`C20A1D0N0x` - прочитать текущее калибровочное смещение
+`C20A2D0N0x` - сбросить калибровку (смещение = 0)</t>
   </si>
 </sst>
 </file>
@@ -1056,7 +1068,7 @@
     <col min="1" max="1" width="12.140625" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
     <col min="3" max="3" width="18.140625" customWidth="1"/>
-    <col min="4" max="4" width="45.28515625" customWidth="1"/>
+    <col min="4" max="4" width="67.140625" customWidth="1"/>
     <col min="5" max="5" width="27.5703125" customWidth="1"/>
     <col min="6" max="7" width="43.85546875" customWidth="1"/>
     <col min="8" max="8" width="8.85546875" customWidth="1"/>
@@ -1424,14 +1436,22 @@
       </c>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
+    <row r="23" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="1">
+        <v>20</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>

--- a/6ch_LED_Driver/Map Registers Control_LED.xlsx
+++ b/6ch_LED_Driver/Map Registers Control_LED.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BAF8ED2-3083-4BEC-B25B-812430A44409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D47D81-5C18-4B51-BB7A-2305480D62F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3180" yWindow="975" windowWidth="21600" windowHeight="12915" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
   <si>
     <t>Десятичная</t>
   </si>
@@ -441,131 +441,6 @@
     <t>0x13</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">C4A1D1N0x
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - комманда
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">A_ - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">режим, 0 одиночный канал,
-1 установка во все каналы  
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">D_ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">- 0 выключить 1 включить
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - имя канала, число от 0 до 5. если  </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, параметр не имннт значение </t>
-    </r>
-  </si>
-  <si>
     <t>Возвращает значение PWM (0-1000)</t>
   </si>
   <si>
@@ -608,6 +483,144 @@
 C20A0D0N0x` - выполнить калибровку нуля (при отключенной нагрузке)
 `C20A1D0N0x` - прочитать текущее калибровочное смещение
 `C20A2D0N0x` - сбросить калибровку (смещение = 0)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C4A1D1N0x
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - комманда
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">A_ - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">режим, 0 одиночный канал,
+1 установка во все каналы  
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">D_ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">- 0 выключить
+ 1 включить
+3 плавный старт канала
+4 плавное гашение канала
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - имя канала, число от 0 до 5. если  </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, параметр не имннт значение </t>
+    </r>
+  </si>
+  <si>
+    <t>C7A0D500N0x</t>
+  </si>
+  <si>
+    <t>fade = 500 мс</t>
+  </si>
+  <si>
+    <t>установить время включения/выключения каналов 
+fade = 500 мс</t>
   </si>
 </sst>
 </file>
@@ -1146,7 +1159,7 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:7" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="160.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -1161,7 +1174,7 @@
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="G7" s="1"/>
     </row>
@@ -1195,7 +1208,7 @@
         <v>29</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
@@ -1203,7 +1216,7 @@
       </c>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -1211,10 +1224,16 @@
         <v>7</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
+      <c r="F10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="11" spans="1:7" ht="79.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
@@ -1227,10 +1246,10 @@
         <v>28</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>47</v>
@@ -1248,7 +1267,7 @@
         <v>30</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
@@ -1256,7 +1275,7 @@
       </c>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
@@ -1286,7 +1305,7 @@
         <v>32</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1" t="s">
@@ -1425,29 +1444,29 @@
         <v>19</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G22" s="1"/>
+    </row>
+    <row r="23" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="G22" s="1"/>
-    </row>
-    <row r="23" spans="1:7" ht="105" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="B23" s="1">
         <v>20</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
